--- a/KatalonData/IWPBootstrapData/vRelayPaymentsACH.xlsx
+++ b/KatalonData/IWPBootstrapData/vRelayPaymentsACH.xlsx
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1337" uniqueCount="213">
   <si>
     <t>Result</t>
   </si>
@@ -552,6 +552,144 @@
   </si>
   <si>
     <t>Fri Nov 21 21:53:16 IST 2025</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 22:31:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 22:36:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 22:37:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 22:41:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 22:53:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 23:05:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 23:29:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 23:32:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 23:35:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 23:38:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 23:40:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 23:43:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 23:46:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 23:49:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 23:52:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 23:55:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jan 21 23:57:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 00:00:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 00:05:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 00:06:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 00:07:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 00:09:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 00:10:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 00:11:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 00:13:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 00:14:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 00:15:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 00:22:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 00:23:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 00:24:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 00:25:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 00:27:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 00:28:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 00:30:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 00:31:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 00:31:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 00:31:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 00:32:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 00:33:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 00:34:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 20:55:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 21:18:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jan 22 21:24:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 23 01:42:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 23 01:45:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jan 23 20:22:02 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -945,7 +1083,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>145</v>
+        <v>195</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1042,7 +1180,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>165</v>
+        <v>206</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1136,7 +1274,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>164</v>
+        <v>205</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1230,7 +1368,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>163</v>
+        <v>204</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1324,7 +1462,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>162</v>
+        <v>203</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1418,7 +1556,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>161</v>
+        <v>201</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1512,7 +1650,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1649,7 +1787,7 @@
         <v>27</v>
       </c>
       <c r="B3" t="s">
-        <v>122</v>
+        <v>212</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
@@ -1745,7 +1883,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>120</v>
+        <v>169</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1836,10 +1974,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>166</v>
+        <v>211</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1930,10 +2068,10 @@
     </row>
     <row ht="29" r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>125</v>
+        <v>209</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2029,7 +2167,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>147</v>
+        <v>196</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2159,10 +2297,10 @@
     </row>
     <row ht="29" r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>124</v>
+        <v>180</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2255,10 +2393,10 @@
     </row>
     <row ht="29" r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>123</v>
+        <v>176</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2357,7 +2495,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>127</v>
+        <v>186</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2449,7 +2587,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>128</v>
+        <v>187</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2541,7 +2679,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>129</v>
+        <v>188</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2633,7 +2771,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>130</v>
+        <v>189</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2725,7 +2863,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>131</v>
+        <v>190</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2909,7 +3047,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>144</v>
+        <v>194</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3036,10 +3174,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>155</v>
+        <v>198</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3130,10 +3268,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>159</v>
+        <v>199</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3224,10 +3362,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>151</v>
+        <v>197</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3318,10 +3456,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>139</v>
+        <v>192</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3412,10 +3550,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>143</v>
+        <v>193</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3506,10 +3644,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>135</v>
+        <v>191</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">

--- a/KatalonData/IWPBootstrapData/vRelayPaymentsACH.xlsx
+++ b/KatalonData/IWPBootstrapData/vRelayPaymentsACH.xlsx
@@ -1,45 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476640\Documents\VPS-Katalon\KatalonData\IWPBootstrapData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476046\Documents\VPS-Katalon-feature-VRelay\KatalonData\IWPBootstrapData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{2FA79759-8B2F-4BB8-B2BC-C584E9741DE3}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr documentId="13_ncr:1_{85B15B76-C419-49F4-B1B4-E3A755DF9337}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView activeTab="15" firstSheet="14" windowHeight="10300" windowWidth="19420" xWindow="-110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-110"/>
+    <workbookView activeTab="3" windowHeight="12456" windowWidth="23256" xWindow="-108" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-108"/>
   </bookViews>
   <sheets>
     <sheet name="PayNowNoCFPC" r:id="rId1" sheetId="1"/>
     <sheet name="PayNowNoCFPS" r:id="rId2" sheetId="2"/>
     <sheet name="PayNowNoCFCorp" r:id="rId3" sheetId="3"/>
-    <sheet name="PayNowSCFPC" r:id="rId4" sheetId="4"/>
-    <sheet name="PayNowSCFPS" r:id="rId5" sheetId="5"/>
-    <sheet name="PayNowSCFCorp" r:id="rId6" sheetId="6"/>
-    <sheet name="PayNowDCFPC" r:id="rId7" sheetId="7"/>
-    <sheet name="PayNowDCFPS" r:id="rId8" sheetId="8"/>
-    <sheet name="PayNowDCFCorp" r:id="rId9" sheetId="9"/>
-    <sheet name="SCFPSVerbiage" r:id="rId10" sheetId="10"/>
-    <sheet name="SCFPCVerbiage" r:id="rId11" sheetId="11"/>
-    <sheet name="SCFCorpVerbiage" r:id="rId12" sheetId="12"/>
-    <sheet name="DCFPSVerbiage" r:id="rId13" sheetId="13"/>
-    <sheet name="DCFPCVerbiage" r:id="rId14" sheetId="14"/>
-    <sheet name="DCFCorpVerbiage" r:id="rId15" sheetId="15"/>
-    <sheet name="CMCAutopayPS" r:id="rId16" sheetId="16"/>
-    <sheet name="CMCAutoPayPC" r:id="rId17" sheetId="17"/>
-    <sheet name="CMCAutoPayCorp" r:id="rId18" sheetId="18"/>
-    <sheet name="CCDeferredPS" r:id="rId19" sheetId="19"/>
-    <sheet name="CCDeferredPC" r:id="rId20" sheetId="20"/>
-    <sheet name="CCDeferredCorp" r:id="rId21" sheetId="21"/>
-    <sheet name="NoModifyAmountPC" r:id="rId22" sheetId="22"/>
-    <sheet name="NoModifyAmountPS" r:id="rId23" sheetId="23"/>
-    <sheet name="NoModifyAmountCorp" r:id="rId24" sheetId="24"/>
-    <sheet name="NoModifyBillingAddressPC" r:id="rId25" sheetId="25"/>
-    <sheet name="NoModifyBillingAddressPS" r:id="rId26" sheetId="26"/>
-    <sheet name="NoModifyBillingAddressCorp" r:id="rId27" sheetId="27"/>
+    <sheet name="PayNowCorpNoCF" r:id="rId4" sheetId="28"/>
+    <sheet name="PayNowSCFPC" r:id="rId5" sheetId="4"/>
+    <sheet name="PayNowSCFPS" r:id="rId6" sheetId="5"/>
+    <sheet name="PayNowSCFCorp" r:id="rId7" sheetId="6"/>
+    <sheet name="PayNowDCFPC" r:id="rId8" sheetId="7"/>
+    <sheet name="PayNowDCFPS" r:id="rId9" sheetId="8"/>
+    <sheet name="PayNowDCFCorp" r:id="rId10" sheetId="9"/>
+    <sheet name="SCFPSVerbiage" r:id="rId11" sheetId="10"/>
+    <sheet name="SCFPCVerbiage" r:id="rId12" sheetId="11"/>
+    <sheet name="SCFCorpVerbiage" r:id="rId13" sheetId="12"/>
+    <sheet name="DCFPSVerbiage" r:id="rId14" sheetId="13"/>
+    <sheet name="DCFPCVerbiage" r:id="rId15" sheetId="14"/>
+    <sheet name="DCFCorpVerbiage" r:id="rId16" sheetId="15"/>
+    <sheet name="CMCAutopayPS" r:id="rId17" sheetId="16"/>
+    <sheet name="CMCAutoPayPC" r:id="rId18" sheetId="17"/>
+    <sheet name="CMCAutoPayCorp" r:id="rId19" sheetId="18"/>
+    <sheet name="CCDeferredPS" r:id="rId20" sheetId="19"/>
+    <sheet name="CCDeferredPC" r:id="rId21" sheetId="20"/>
+    <sheet name="CCDeferredCorp" r:id="rId22" sheetId="21"/>
+    <sheet name="NoModifyAmountPC" r:id="rId23" sheetId="22"/>
+    <sheet name="NoModifyAmountPS" r:id="rId24" sheetId="23"/>
+    <sheet name="NoModifyAmountCorp" r:id="rId25" sheetId="24"/>
+    <sheet name="NoModifyBillingAddressPC" r:id="rId26" sheetId="25"/>
+    <sheet name="NoModifyBillingAddressPS" r:id="rId27" sheetId="26"/>
+    <sheet name="NoModifyBillingAddressCorp" r:id="rId28" sheetId="27"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -51,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1337" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1901" uniqueCount="348">
   <si>
     <t>Result</t>
   </si>
@@ -155,541 +156,946 @@
     <t>Wed Mar 26 17:31:49 IST 2025</t>
   </si>
   <si>
-    <t>Wed Mar 26 18:52:38 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Mar 26 18:55:20 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 00:28:35 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 00:30:00 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 00:31:10 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 00:44:51 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 00:46:57 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 00:49:01 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 00:50:00 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 00:50:55 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 00:52:42 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 00:53:35 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 00:54:25 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 01:00:05 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 01:02:28 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 01:03:15 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 01:04:56 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 01:05:51 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 01:06:41 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 01:08:10 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 01:08:51 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 01:09:17 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 01:10:40 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 01:11:20 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 01:12:02 IST 2025</t>
-  </si>
-  <si>
     <t>33</t>
   </si>
   <si>
+    <t>Wed Feb 04 13:09:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 04 14:51:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 04 14:53:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 04 14:56:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 04 15:05:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 04 15:15:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 04 15:16:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 04 15:20:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 04 15:26:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 04 15:27:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 04 15:30:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 04 16:18:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 04 16:22:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 04 16:28:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 04 16:32:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 04 16:33:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 04 16:36:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 04 16:38:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 04 16:39:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 04 16:39:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 04 16:40:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 04 16:41:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 04 16:42:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 04 20:33:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 04 20:36:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 04 21:00:21 IST 2026</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Fri Aug 29 22:56:00 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 22:57:20 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 22:58:47 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 23:07:05 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 23:08:03 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 23:08:58 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 23:10:53 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 23:11:52 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 23:12:56 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 23:14:46 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 23:15:37 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 23:16:30 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 23:22:19 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 23:23:04 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 23:23:54 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 23:25:34 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 23:26:21 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 23:27:12 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 23:28:38 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 23:29:22 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 23:29:44 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 23:31:04 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 23:31:51 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Aug 29 23:32:29 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 02 01:16:14 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 02 01:17:43 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 02 01:19:04 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 02 09:07:24 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 02 09:08:51 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 02 09:10:04 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 02 11:11:25 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 02 11:12:56 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 02 11:14:11 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 02 11:16:42 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 02 11:20:27 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 02 11:23:11 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 02 11:24:17 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 02 11:25:18 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 02 11:27:18 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 02 11:28:19 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 02 11:29:16 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 02 11:31:22 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 02 11:32:16 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 02 11:33:09 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 02 11:38:54 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 02 11:39:46 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 02 11:40:37 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 02 11:43:54 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 02 11:44:45 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 02 11:45:37 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 02 11:47:17 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 02 11:47:57 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 02 11:48:18 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 02 11:49:30 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 02 11:50:10 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 02 11:51:00 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Sep 02 13:16:52 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 00:29:40 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 00:30:59 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 00:32:52 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 00:36:13 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 00:49:28 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 01:13:04 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 01:14:37 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 01:15:56 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 01:18:35 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 01:19:42 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 01:20:52 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 01:23:14 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 01:24:21 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 01:25:29 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 01:35:20 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 01:37:32 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 01:39:38 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 01:41:49 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 01:44:01 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 01:46:10 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 01:48:17 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 01:50:28 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 01:52:42 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 01:54:47 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 01:56:45 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 01:58:50 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 02:06:28 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 02:07:24 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 02:08:33 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 02:11:00 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 02:20:35 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 02:22:38 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 02:24:34 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 02:26:52 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 02:28:48 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 02:30:46 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 02:32:53 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 02:34:53 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 02:36:59 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 02:38:57 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 02:40:59 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 02:42:57 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 02:46:26 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 02:47:09 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 02:47:40 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 02:49:28 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 02:50:34 IST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 18 02:51:15 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 21 21:53:16 IST 2025</t>
-  </si>
-  <si>
-    <t>Wed Jan 21 22:31:10 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jan 21 22:36:05 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jan 21 22:37:49 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jan 21 22:41:02 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jan 21 22:53:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jan 21 23:05:10 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jan 21 23:29:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jan 21 23:32:13 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jan 21 23:35:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jan 21 23:38:02 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jan 21 23:40:59 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jan 21 23:43:46 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jan 21 23:46:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jan 21 23:49:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jan 21 23:52:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jan 21 23:55:03 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jan 21 23:57:56 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 00:00:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 00:05:02 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 00:06:03 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 00:07:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 00:09:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 00:10:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 00:11:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 00:13:55 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 00:14:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 00:15:48 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 00:22:03 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 00:23:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 00:24:02 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 00:25:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 00:27:02 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 00:28:03 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 00:30:30 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 00:31:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 00:31:35 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 00:31:55 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 00:32:54 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 00:33:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 00:34:15 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 20:55:59 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 21:18:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jan 22 21:24:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 23 01:42:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 23 01:45:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Jan 23 20:22:02 IST 2026</t>
+    <t>Thu Feb 12 00:54:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 01:03:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 01:15:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 01:28:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 01:40:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 01:44:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 01:47:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 01:48:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 01:51:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 01:53:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 01:56:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 01:59:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:02:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:04:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:07:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:10:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:12:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:16:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:17:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:19:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:21:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:22:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:23:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:26:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:27:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:28:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:36:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:37:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:38:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:40:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:41:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:42:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:44:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:45:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:46:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:46:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:48:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:49:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:50:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:51:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 02:52:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 20:04:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 20:07:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 20:33:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 12 21:37:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Feb 13 19:33:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 16 21:05:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 16 22:36:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 16 23:25:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 16 23:33:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 00:32:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 00:37:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 20:30:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 22:28:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 22:31:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Feb 18 22:42:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 01:11:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 01:13:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 01:19:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 01:34:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 01:57:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 01:59:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:00:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:01:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:03:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:05:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:06:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:07:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:09:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:10:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:11:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:13:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:14:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:15:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:22:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:22:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:23:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:27:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:28:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:29:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:31:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:31:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:32:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:33:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:34:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:35:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:48:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 02:52:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 03:07:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 03:19:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 03:31:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 03:56:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 03:57:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 03:59:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:00:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:05:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:06:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:07:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:09:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:11:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:12:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:14:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:15:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:16:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:23:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:25:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:26:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:28:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:29:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:30:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:32:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:33:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:33:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:34:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:35:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:37:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:46:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:48:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:50:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:53:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:55:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 04:56:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 05:12:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 05:13:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 05:15:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 05:17:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 05:18:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 05:19:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 05:22:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 05:23:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 05:24:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 05:30:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 05:31:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 05:33:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 05:35:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 05:36:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 05:37:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 05:39:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 05:41:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 05:44:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 05:46:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 05:48:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 05:54:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 05:57:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 05:59:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 06:01:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 06:03:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 06:06:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 06:06:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 06:07:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 06:12:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 06:13:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 06:13:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Feb 19 18:07:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 01:52:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 01:55:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 01:57:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 02:00:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 02:01:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 02:02:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 02:06:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 02:07:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 02:08:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 02:10:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 02:26:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 02:28:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 02:29:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 02:30:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 02:32:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 02:33:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 02:34:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 02:40:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 02:41:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 02:42:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 02:43:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 02:44:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 02:45:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 02:47:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 02:49:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 02:50:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 02:52:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 02:58:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 03:04:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 03:06:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 03:08:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 03:10:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 03:13:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 03:17:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 03:20:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 03:21:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 03:22:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 03:22:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 03:36:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 03:37:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 03:38:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 07:31:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 21 07:51:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 20:30:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 20:34:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 21:51:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 24 21:54:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 06:48:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 06:59:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 07:04:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 07:08:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 07:20:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 07:22:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 07:35:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 07:47:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 08:21:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 08:22:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 08:24:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 08:25:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 08:27:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 08:28:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 08:32:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 08:33:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 08:34:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 08:36:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 08:38:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 08:39:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 08:40:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 08:41:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 08:42:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 08:48:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 08:49:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 08:50:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 08:52:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 08:53:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 08:54:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 09:04:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 09:10:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 09:16:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 09:22:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 09:24:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 09:26:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 09:27:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 09:51:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 09:53:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 10:01:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 10:08:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 10:17:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 10:19:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 10:20:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 10:20:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 10:22:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 10:23:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 10:23:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Feb 28 10:24:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 03 00:23:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 03 00:47:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 14:09:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 14:37:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 14:41:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 15:09:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 04 15:32:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 22:00:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 22:06:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 22:12:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 22:19:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 22:25:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 22:30:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 11 22:49:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 12 19:42:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 12 19:46:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 12 19:53:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 12 19:59:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 12 20:21:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 12 20:23:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 12 20:28:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 12 20:31:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 12 20:34:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 12 21:24:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 12 21:30:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 12 21:31:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 12 21:36:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 12 21:45:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Mar 13 21:50:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Mar 16 20:46:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Mar 16 22:15:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 17 20:45:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 17 21:00:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 18 20:44:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 19 00:27:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 19 00:48:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 19 20:38:27 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1029,12 +1435,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="8.453125" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="8.44140625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="29" r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1078,12 +1484,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>195</v>
+        <v>329</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1127,11 +1533,11 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4906B75B-52A2-4286-8E49-5AC0D3846EF6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11E0D7D6-07EB-4231-93F6-ED08F4FB8116}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1175,12 +1581,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>206</v>
+        <v>283</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1190,7 +1596,7 @@
         <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>17</v>
@@ -1202,17 +1608,17 @@
         <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1221,11 +1627,11 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A8CFE94-49D0-484F-8EA4-D25F286F5569}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4906B75B-52A2-4286-8E49-5AC0D3846EF6}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1269,12 +1675,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>205</v>
+        <v>310</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1299,7 +1705,7 @@
         <v>20</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
@@ -1315,11 +1721,11 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAAC6231-DFFA-4867-A2C5-E804FC85451E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A8CFE94-49D0-484F-8EA4-D25F286F5569}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1363,12 +1769,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>204</v>
+        <v>309</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1390,10 +1796,10 @@
         <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
@@ -1409,11 +1815,11 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F82C58E-06FC-4FC1-A08F-B42071E415C5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAAC6231-DFFA-4867-A2C5-E804FC85451E}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1457,12 +1863,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>203</v>
+        <v>307</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1472,7 +1878,7 @@
         <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>17</v>
@@ -1484,10 +1890,10 @@
         <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
@@ -1503,11 +1909,11 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1142462-EBF3-4DC6-A60C-82C83F380CA2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F82C58E-06FC-4FC1-A08F-B42071E415C5}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1551,12 +1957,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>201</v>
+        <v>336</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1581,7 +1987,7 @@
         <v>20</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
@@ -1597,11 +2003,11 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADDD6D56-27E0-426C-B504-18A7A35ECE43}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1142462-EBF3-4DC6-A60C-82C83F380CA2}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1645,12 +2051,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>200</v>
+        <v>335</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1672,10 +2078,10 @@
         <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
@@ -1691,14 +2097,11 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C8655E4-5A57-47F0-9C21-BF6A0B57A685}">
-  <dimension ref="A1:O3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="26.36328125" collapsed="true"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADDD6D56-27E0-426C-B504-18A7A35ECE43}">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1742,22 +2145,22 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>334</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>17</v>
@@ -1769,55 +2172,16 @@
         <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
         <v>23</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" t="s">
-        <v>212</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="N3" s="2" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1827,14 +2191,14 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A154E49-E158-4463-B5C3-6CDEA93CBDB2}">
-  <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C8655E4-5A57-47F0-9C21-BF6A0B57A685}">
+  <dimension ref="A1:O3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="26.36328125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="26.33203125" collapsed="true"/>
   </cols>
   <sheetData>
-    <row ht="29" r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1878,16 +2242,16 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>169</v>
+        <v>33</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>28</v>
@@ -1908,13 +2272,52 @@
         <v>20</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
         <v>23</v>
       </c>
       <c r="N2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
+        <v>319</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" s="2" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1924,11 +2327,14 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACEC2CC9-16AB-47E7-916A-C86EFB95B8FF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A154E49-E158-4463-B5C3-6CDEA93CBDB2}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="26.33203125" collapsed="true"/>
+  </cols>
   <sheetData>
-    <row ht="29" r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1972,12 +2378,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>211</v>
+        <v>343</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1999,10 +2405,10 @@
         <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
@@ -2018,11 +2424,11 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAB20633-2C53-43C5-A793-14D961E78E27}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACEC2CC9-16AB-47E7-916A-C86EFB95B8FF}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2066,19 +2472,19 @@
         <v>12</v>
       </c>
     </row>
-    <row ht="29" r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>209</v>
+        <v>341</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>16</v>
@@ -2093,19 +2499,17 @@
         <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>30</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -2116,9 +2520,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31792679-2814-4031-94D5-F81C214E87F1}">
   <dimension ref="A1:O3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2162,12 +2566,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>196</v>
+        <v>330</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2202,7 +2606,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -2244,14 +2648,11 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{799F2BD1-FD78-448F-ADE0-45642B43D84A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAB20633-2C53-43C5-A793-14D961E78E27}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="26.0" collapsed="true"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2295,12 +2696,12 @@
         <v>12</v>
       </c>
     </row>
-    <row ht="29" r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>180</v>
+        <v>323</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2325,16 +2726,16 @@
         <v>20</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -2343,11 +2744,14 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29FE3965-D54B-4EAB-9FD8-877E447C190D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{799F2BD1-FD78-448F-ADE0-45642B43D84A}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="26.0" collapsed="true"/>
+  </cols>
   <sheetData>
-    <row ht="29" r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2391,12 +2795,12 @@
         <v>12</v>
       </c>
     </row>
-    <row ht="29" r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>176</v>
+        <v>347</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2418,19 +2822,19 @@
         <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -2439,14 +2843,11 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9AD100D-0DBC-45F3-A121-6F02543E9C7F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29FE3965-D54B-4EAB-9FD8-877E447C190D}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="23.7265625" collapsed="true"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2490,12 +2891,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>186</v>
+        <v>345</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2505,22 +2906,26 @@
         <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="1"/>
+      <c r="H2" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="I2" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="L2" s="1"/>
+        <v>18</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="M2" s="1" t="s">
         <v>18</v>
       </c>
@@ -2534,11 +2939,14 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0B1942B-E20C-4A56-9017-395FE3466CCA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9AD100D-0DBC-45F3-A121-6F02543E9C7F}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="23.77734375" collapsed="true"/>
+  </cols>
   <sheetData>
-    <row ht="29" r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2582,12 +2990,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>187</v>
+        <v>278</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2610,7 +3018,7 @@
         <v>20</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
@@ -2626,11 +3034,11 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{800664F6-7B82-4E54-A9A3-002FB30EA5CC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0B1942B-E20C-4A56-9017-395FE3466CCA}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2674,12 +3082,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>188</v>
+        <v>279</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2699,10 +3107,10 @@
         <v>23</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
@@ -2718,11 +3126,11 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AFA7D1E-C4C8-4F11-85C1-FED8E36A55A8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{800664F6-7B82-4E54-A9A3-002FB30EA5CC}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2766,12 +3174,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>189</v>
+        <v>325</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2791,10 +3199,10 @@
         <v>23</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
@@ -2810,11 +3218,11 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0002C261-402A-419B-8856-C464A90C3C50}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AFA7D1E-C4C8-4F11-85C1-FED8E36A55A8}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2858,12 +3266,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>190</v>
+        <v>281</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2886,7 +3294,7 @@
         <v>20</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
@@ -2902,11 +3310,103 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0002C261-402A-419B-8856-C464A90C3C50}">
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>326</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2342668C-48CF-464B-9A5B-74841457CAE0}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2950,7 +3450,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -2996,9 +3496,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62C3F18C-9D20-495D-9813-3EBF52ED12D9}">
   <dimension ref="A1:O3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3042,12 +3542,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>194</v>
+        <v>328</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3082,7 +3582,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -3124,11 +3624,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C787DE57-842A-41F3-A622-37CAD141F86A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2966B24D-47B9-4F80-A7B5-23FEBF76DFC5}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3172,12 +3672,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>198</v>
+        <v>46</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3187,7 +3687,7 @@
         <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>17</v>
@@ -3199,17 +3699,17 @@
         <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -3218,11 +3718,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4D9E566-D549-4290-8382-839D19B358D4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C787DE57-842A-41F3-A622-37CAD141F86A}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3266,12 +3766,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>199</v>
+        <v>332</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3296,14 +3796,14 @@
         <v>20</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -3312,11 +3812,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06A1626C-D7FE-41AC-B701-168C96807B23}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4D9E566-D549-4290-8382-839D19B358D4}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3360,12 +3860,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>197</v>
+        <v>333</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3387,10 +3887,10 @@
         <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
@@ -3406,11 +3906,11 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BDBB12C-A1A3-4DC3-80BE-B879BD79EAD4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06A1626C-D7FE-41AC-B701-168C96807B23}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3454,12 +3954,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>192</v>
+        <v>331</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3469,7 +3969,7 @@
         <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>17</v>
@@ -3481,17 +3981,17 @@
         <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -3500,11 +4000,11 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C84570EB-6A55-4CD3-91DD-65D15A5DA7B9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BDBB12C-A1A3-4DC3-80BE-B879BD79EAD4}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3548,12 +4048,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>193</v>
+        <v>284</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3578,14 +4078,14 @@
         <v>20</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -3594,11 +4094,11 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11E0D7D6-07EB-4231-93F6-ED08F4FB8116}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C84570EB-6A55-4CD3-91DD-65D15A5DA7B9}">
   <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="29" r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3642,12 +4142,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>191</v>
+        <v>327</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3669,10 +4169,10 @@
         <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">

--- a/KatalonData/IWPBootstrapData/vRelayPaymentsACH.xlsx
+++ b/KatalonData/IWPBootstrapData/vRelayPaymentsACH.xlsx
@@ -1,50 +1,70 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476046\Documents\VPS-Katalon-feature-VRelay\KatalonData\IWPBootstrapData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{85B15B76-C419-49F4-B1B4-E3A755DF9337}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABD0496D-E0D4-44AE-A8C2-30962159A40A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="3" windowHeight="12456" windowWidth="23256" xWindow="-108" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-108"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="PayNowNoCFPC" r:id="rId1" sheetId="1"/>
-    <sheet name="PayNowNoCFPS" r:id="rId2" sheetId="2"/>
-    <sheet name="PayNowNoCFCorp" r:id="rId3" sheetId="3"/>
-    <sheet name="PayNowCorpNoCF" r:id="rId4" sheetId="28"/>
-    <sheet name="PayNowSCFPC" r:id="rId5" sheetId="4"/>
-    <sheet name="PayNowSCFPS" r:id="rId6" sheetId="5"/>
-    <sheet name="PayNowSCFCorp" r:id="rId7" sheetId="6"/>
-    <sheet name="PayNowDCFPC" r:id="rId8" sheetId="7"/>
-    <sheet name="PayNowDCFPS" r:id="rId9" sheetId="8"/>
-    <sheet name="PayNowDCFCorp" r:id="rId10" sheetId="9"/>
-    <sheet name="SCFPSVerbiage" r:id="rId11" sheetId="10"/>
-    <sheet name="SCFPCVerbiage" r:id="rId12" sheetId="11"/>
-    <sheet name="SCFCorpVerbiage" r:id="rId13" sheetId="12"/>
-    <sheet name="DCFPSVerbiage" r:id="rId14" sheetId="13"/>
-    <sheet name="DCFPCVerbiage" r:id="rId15" sheetId="14"/>
-    <sheet name="DCFCorpVerbiage" r:id="rId16" sheetId="15"/>
-    <sheet name="CMCAutopayPS" r:id="rId17" sheetId="16"/>
-    <sheet name="CMCAutoPayPC" r:id="rId18" sheetId="17"/>
-    <sheet name="CMCAutoPayCorp" r:id="rId19" sheetId="18"/>
-    <sheet name="CCDeferredPS" r:id="rId20" sheetId="19"/>
-    <sheet name="CCDeferredPC" r:id="rId21" sheetId="20"/>
-    <sheet name="CCDeferredCorp" r:id="rId22" sheetId="21"/>
-    <sheet name="NoModifyAmountPC" r:id="rId23" sheetId="22"/>
-    <sheet name="NoModifyAmountPS" r:id="rId24" sheetId="23"/>
-    <sheet name="NoModifyAmountCorp" r:id="rId25" sheetId="24"/>
-    <sheet name="NoModifyBillingAddressPC" r:id="rId26" sheetId="25"/>
-    <sheet name="NoModifyBillingAddressPS" r:id="rId27" sheetId="26"/>
-    <sheet name="NoModifyBillingAddressCorp" r:id="rId28" sheetId="27"/>
+    <sheet name="PayNowNoCFPC" sheetId="1" r:id="rId1"/>
+    <sheet name="PayNowNoCFPS" sheetId="2" r:id="rId2"/>
+    <sheet name="PayNowNoCFCorp" sheetId="3" r:id="rId3"/>
+    <sheet name="VerifyPaymentConfCorp" sheetId="45" r:id="rId4"/>
+    <sheet name="VerifyPaymentReceiptPC" sheetId="49" r:id="rId5"/>
+    <sheet name="VerifyPaymentConfPC" sheetId="46" r:id="rId6"/>
+    <sheet name="PayNowCorpNoCF" sheetId="28" r:id="rId7"/>
+    <sheet name="VerifyPaymentReceiptCorp" sheetId="48" r:id="rId8"/>
+    <sheet name="PayNowSCFPC" sheetId="4" r:id="rId9"/>
+    <sheet name="PayNowSCFPS" sheetId="5" r:id="rId10"/>
+    <sheet name="PayNowSCFCorp" sheetId="6" r:id="rId11"/>
+    <sheet name="PayNowDCFPC" sheetId="7" r:id="rId12"/>
+    <sheet name="PayNowDCFPS" sheetId="8" r:id="rId13"/>
+    <sheet name="PayNowDCFCorp" sheetId="9" r:id="rId14"/>
+    <sheet name="SCFPSVerbiage" sheetId="10" r:id="rId15"/>
+    <sheet name="SCFPCVerbiage" sheetId="11" r:id="rId16"/>
+    <sheet name="SCFCorpVerbiage" sheetId="12" r:id="rId17"/>
+    <sheet name="DCFPSVerbiage" sheetId="13" r:id="rId18"/>
+    <sheet name="DCFPCVerbiage" sheetId="14" r:id="rId19"/>
+    <sheet name="DCFCorpVerbiage" sheetId="15" r:id="rId20"/>
+    <sheet name="CMCAutopayPS" sheetId="16" r:id="rId21"/>
+    <sheet name="CMCAutoPayPC" sheetId="17" r:id="rId22"/>
+    <sheet name="CancelStaticTextAutopayPC" sheetId="37" r:id="rId23"/>
+    <sheet name="CancelSuccessAutopayPC" sheetId="38" r:id="rId24"/>
+    <sheet name="ModifyStaticTextAutopayPC" sheetId="39" r:id="rId25"/>
+    <sheet name="ModifySuccessAutopayPC" sheetId="40" r:id="rId26"/>
+    <sheet name="CMCAutoPayCorp" sheetId="18" r:id="rId27"/>
+    <sheet name="CancelStaticTextAutoPayCorp" sheetId="29" r:id="rId28"/>
+    <sheet name="CancelSuccessAutoPayCorp" sheetId="30" r:id="rId29"/>
+    <sheet name="ModifyStaticTextAutopayCorp" sheetId="31" r:id="rId30"/>
+    <sheet name="ModifySuccessAutopayCorp" sheetId="32" r:id="rId31"/>
+    <sheet name="CCDeferredPS" sheetId="19" r:id="rId32"/>
+    <sheet name="CCDeferredPC" sheetId="20" r:id="rId33"/>
+    <sheet name="CancelStaticTextDeferredPC" sheetId="41" r:id="rId34"/>
+    <sheet name="CancelSuccessDeferredPC" sheetId="42" r:id="rId35"/>
+    <sheet name="ModifyStaticTextDeferredPC" sheetId="43" r:id="rId36"/>
+    <sheet name="ModifySuccessDeferredPC" sheetId="44" r:id="rId37"/>
+    <sheet name="CCDeferredCorp" sheetId="21" r:id="rId38"/>
+    <sheet name="CancelStaticTextDeferredCorp" sheetId="33" r:id="rId39"/>
+    <sheet name="CancelSuccessDeferredCorp" sheetId="34" r:id="rId40"/>
+    <sheet name="ModifyStaticTextDeferredCorp" sheetId="35" r:id="rId41"/>
+    <sheet name="ModifySuccessDeferredCorp" sheetId="36" r:id="rId42"/>
+    <sheet name="NoModifyAmountPC" sheetId="22" r:id="rId43"/>
+    <sheet name="NoModifyAmountPS" sheetId="23" r:id="rId44"/>
+    <sheet name="NoModifyAmountCorp" sheetId="24" r:id="rId45"/>
+    <sheet name="NoModifyBillingAddressPC" sheetId="25" r:id="rId46"/>
+    <sheet name="NoModifyBillingAddressPS" sheetId="26" r:id="rId47"/>
+    <sheet name="NoModifyBillingAddressCorp" sheetId="27" r:id="rId48"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -52,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1901" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1283" uniqueCount="68">
   <si>
     <t>Result</t>
   </si>
@@ -159,879 +179,39 @@
     <t>33</t>
   </si>
   <si>
-    <t>Wed Feb 04 13:09:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 14:51:31 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 14:53:10 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 14:56:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 15:05:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 15:15:36 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 15:16:49 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 15:20:54 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 15:26:07 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 15:27:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 15:30:37 IST 2026</t>
-  </si>
-  <si>
     <t>Wed Feb 04 16:18:37 IST 2026</t>
   </si>
   <si>
-    <t>Wed Feb 04 16:22:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 16:28:04 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 16:32:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 16:33:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 16:36:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 16:38:20 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 16:39:04 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 16:39:33 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 16:40:41 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 16:41:26 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 16:42:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 20:33:36 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 20:36:48 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 21:00:21 IST 2026</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Thu Feb 12 00:54:43 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 01:03:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 01:15:56 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 01:28:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 01:40:36 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 01:44:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 01:47:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 01:48:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 01:51:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 01:53:58 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 01:56:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 01:59:36 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 02:02:09 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 02:04:55 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 02:07:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 02:10:01 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 02:12:31 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 02:16:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 02:17:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 02:19:16 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 02:21:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 02:22:43 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 02:23:54 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 02:26:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 02:27:14 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 02:28:16 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 02:36:12 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 02:37:16 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 02:38:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 02:40:31 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 02:41:31 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 02:42:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 02:44:59 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 02:45:56 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 02:46:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 02:46:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 02:48:26 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 02:49:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 02:50:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 02:51:36 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 02:52:36 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 20:04:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 20:07:27 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 20:33:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 12 21:37:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Feb 13 19:33:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 16 21:05:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 16 22:36:30 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 16 23:25:45 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 16 23:33:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 00:32:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 00:37:04 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 18 20:30:55 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 18 22:28:09 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 18 22:31:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 18 22:42:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 01:11:13 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 01:13:40 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 01:19:27 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 01:34:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 01:57:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 01:59:03 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 02:00:20 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 02:01:39 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 02:03:04 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 02:05:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 02:06:30 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 02:07:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 02:09:40 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 02:10:42 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 02:11:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 02:13:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 02:14:46 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 02:15:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 02:22:02 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 02:22:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 02:23:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 02:27:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 02:28:33 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 02:29:31 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 02:31:16 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 02:31:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 02:32:27 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 02:33:41 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 02:34:42 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 02:35:33 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 02:48:09 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 02:52:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 03:07:39 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 03:19:43 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 03:31:48 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 03:56:03 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 03:57:40 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 03:59:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 04:00:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 04:05:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 04:06:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 04:07:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 04:09:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 04:11:05 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 04:12:14 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 04:14:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 04:15:31 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 04:16:31 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 04:23:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 04:25:01 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 04:26:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 04:28:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 04:29:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 04:30:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 04:32:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 04:33:10 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 04:33:35 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 04:34:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 04:35:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 04:37:10 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 04:46:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 04:48:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 04:50:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 04:53:23 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 04:55:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 04:56:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 05:12:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 05:13:55 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 05:15:05 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 05:17:26 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 05:18:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 05:19:55 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 05:22:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 05:23:04 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 05:24:15 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 05:30:56 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 05:31:58 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 05:33:02 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 05:35:15 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 05:36:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 05:37:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 05:39:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 05:41:54 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 05:44:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 05:46:07 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 05:48:14 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 05:54:42 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 05:57:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 05:59:12 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 06:01:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 06:03:30 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 06:06:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 06:06:48 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 06:07:07 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 06:12:12 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 06:13:03 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 06:13:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 19 18:07:03 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 01:52:35 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 01:55:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 01:57:15 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 02:00:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 02:01:26 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 02:02:41 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 02:06:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 02:07:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 02:08:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 02:10:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 02:26:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 02:28:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 02:29:48 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 02:30:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 02:32:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 02:33:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 02:34:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 02:40:26 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 02:41:13 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 02:42:04 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 02:43:42 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 02:44:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 02:45:26 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 02:47:20 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 02:49:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 02:50:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 02:52:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 02:58:54 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 03:04:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 03:06:20 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 03:08:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 03:10:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 03:13:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 03:17:09 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 03:20:58 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 03:21:42 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 03:22:03 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 03:22:27 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 03:36:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 03:37:03 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 03:38:20 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 07:31:35 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 21 07:51:30 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 20:30:39 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 20:34:07 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 24 21:51:20 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 24 21:54:01 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 28 06:48:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 28 06:59:30 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 28 07:04:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 28 07:08:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 28 07:20:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 28 07:22:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 28 07:35:39 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 28 07:47:35 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 28 08:21:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 28 08:22:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 28 08:24:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 28 08:25:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 28 08:27:07 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 28 08:28:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 28 08:32:36 IST 2026</t>
-  </si>
-  <si>
     <t>Sat Feb 28 08:33:42 IST 2026</t>
   </si>
   <si>
     <t>Sat Feb 28 08:34:51 IST 2026</t>
   </si>
   <si>
-    <t>Sat Feb 28 08:36:56 IST 2026</t>
-  </si>
-  <si>
     <t>Sat Feb 28 08:38:01 IST 2026</t>
   </si>
   <si>
-    <t>Sat Feb 28 08:39:03 IST 2026</t>
-  </si>
-  <si>
     <t>Sat Feb 28 08:40:56 IST 2026</t>
   </si>
   <si>
     <t>Sat Feb 28 08:41:51 IST 2026</t>
   </si>
   <si>
-    <t>Sat Feb 28 08:42:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 28 08:48:59 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 28 08:49:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 28 08:50:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 28 08:52:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 28 08:53:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 28 08:54:42 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 28 09:04:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 28 09:10:33 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 28 09:16:49 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 28 09:22:49 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 28 09:24:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 28 09:26:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 28 09:27:56 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 28 09:51:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 28 09:53:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 28 10:01:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 28 10:08:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 28 10:17:59 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 28 10:19:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 28 10:20:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Feb 28 10:20:51 IST 2026</t>
-  </si>
-  <si>
     <t>Sat Feb 28 10:22:35 IST 2026</t>
   </si>
   <si>
-    <t>Sat Feb 28 10:23:15 IST 2026</t>
-  </si>
-  <si>
     <t>Sat Feb 28 10:23:53 IST 2026</t>
   </si>
   <si>
     <t>Sat Feb 28 10:24:44 IST 2026</t>
   </si>
   <si>
-    <t>Tue Mar 03 00:23:48 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 03 00:47:09 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 04 14:09:49 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 04 14:37:58 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 04 14:41:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 04 15:09:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 04 15:32:49 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 22:00:44 IST 2026</t>
-  </si>
-  <si>
     <t>Wed Mar 11 22:06:08 IST 2026</t>
   </si>
   <si>
-    <t>Wed Mar 11 22:12:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 22:19:41 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 22:25:05 IST 2026</t>
-  </si>
-  <si>
     <t>Wed Mar 11 22:30:18 IST 2026</t>
   </si>
   <si>
-    <t>Wed Mar 11 22:49:30 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Mar 12 19:42:39 IST 2026</t>
-  </si>
-  <si>
     <t>Thu Mar 12 19:46:21 IST 2026</t>
   </si>
   <si>
@@ -1059,50 +239,49 @@
     <t>Thu Mar 12 21:24:33 IST 2026</t>
   </si>
   <si>
-    <t>Thu Mar 12 21:30:11 IST 2026</t>
-  </si>
-  <si>
     <t>Thu Mar 12 21:31:12 IST 2026</t>
   </si>
   <si>
-    <t>Thu Mar 12 21:36:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Mar 12 21:45:23 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Mar 13 21:50:48 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Mar 16 20:46:41 IST 2026</t>
-  </si>
-  <si>
     <t>Mon Mar 16 22:15:02 IST 2026</t>
   </si>
   <si>
-    <t>Tue Mar 17 20:45:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Mar 17 21:00:16 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 18 20:44:45 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Mar 19 00:27:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Mar 19 00:48:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Mar 19 20:38:27 IST 2026</t>
+    <t>Tue Mar 24 20:25:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 19:20:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 20:26:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 31 19:13:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 31 20:45:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 31 20:53:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Mar 31 20:58:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Apr 01 18:39:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 02 19:45:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 03 20:02:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 06 21:44:56 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1145,21 +324,21 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0"/>
-    <xf applyBorder="1" borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1176,10 +355,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -1214,7 +393,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1249,7 +428,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1343,21 +522,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -1374,7 +553,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -1426,21 +605,21 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="8.44140625" collapsed="true"/>
+    <col min="5" max="5" width="8.44140625" bestFit="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1489,7 +668,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>329</v>
+        <v>49</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1525,7 +704,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -1533,11 +712,11 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11E0D7D6-07EB-4231-93F6-ED08F4FB8116}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4D9E566-D549-4290-8382-839D19B358D4}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1586,7 +765,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>283</v>
+        <v>53</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1596,7 +775,7 @@
         <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>17</v>
@@ -1608,10 +787,10 @@
         <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
@@ -1622,16 +801,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4906B75B-52A2-4286-8E49-5AC0D3846EF6}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06A1626C-D7FE-41AC-B701-168C96807B23}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1680,7 +859,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>310</v>
+        <v>51</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1702,30 +881,30 @@
         <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A8CFE94-49D0-484F-8EA4-D25F286F5569}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BDBB12C-A1A3-4DC3-80BE-B879BD79EAD4}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1774,7 +953,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>309</v>
+        <v>40</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1784,7 +963,7 @@
         <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>17</v>
@@ -1806,20 +985,20 @@
         <v>23</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAAC6231-DFFA-4867-A2C5-E804FC85451E}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C84570EB-6A55-4CD3-91DD-65D15A5DA7B9}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1868,7 +1047,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>307</v>
+        <v>47</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1878,7 +1057,7 @@
         <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>17</v>
@@ -1890,30 +1069,30 @@
         <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F82C58E-06FC-4FC1-A08F-B42071E415C5}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11E0D7D6-07EB-4231-93F6-ED08F4FB8116}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1962,7 +1141,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>336</v>
+        <v>39</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1984,30 +1163,30 @@
         <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1142462-EBF3-4DC6-A60C-82C83F380CA2}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4906B75B-52A2-4286-8E49-5AC0D3846EF6}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2056,7 +1235,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>335</v>
+        <v>43</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2066,7 +1245,7 @@
         <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>17</v>
@@ -2081,7 +1260,7 @@
         <v>20</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
@@ -2092,16 +1271,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADDD6D56-27E0-426C-B504-18A7A35ECE43}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A8CFE94-49D0-484F-8EA4-D25F286F5569}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2150,7 +1329,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>334</v>
+        <v>42</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2160,7 +1339,7 @@
         <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>17</v>
@@ -2172,10 +1351,10 @@
         <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
@@ -2186,19 +1365,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C8655E4-5A57-47F0-9C21-BF6A0B57A685}">
-  <dimension ref="A1:O3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAAC6231-DFFA-4867-A2C5-E804FC85451E}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="26.33203125" collapsed="true"/>
-  </cols>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2244,20 +1420,20 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>17</v>
@@ -2269,10 +1445,10 @@
         <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
@@ -2282,59 +1458,17 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" t="s">
-        <v>319</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A154E49-E158-4463-B5C3-6CDEA93CBDB2}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F82C58E-06FC-4FC1-A08F-B42071E415C5}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="26.33203125" collapsed="true"/>
-  </cols>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2383,17 +1517,17 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>343</v>
+        <v>55</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>17</v>
@@ -2408,7 +1542,7 @@
         <v>20</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
@@ -2419,16 +1553,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACEC2CC9-16AB-47E7-916A-C86EFB95B8FF}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1142462-EBF3-4DC6-A60C-82C83F380CA2}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2477,17 +1611,17 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>341</v>
+        <v>66</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>17</v>
@@ -2499,10 +1633,10 @@
         <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
@@ -2513,16 +1647,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31792679-2814-4031-94D5-F81C214E87F1}">
-  <dimension ref="A1:O3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31792679-2814-4031-94D5-F81C214E87F1}">
+  <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2571,7 +1705,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>330</v>
+        <v>50</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2643,16 +1777,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAB20633-2C53-43C5-A793-14D961E78E27}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADDD6D56-27E0-426C-B504-18A7A35ECE43}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2696,12 +1830,12 @@
         <v>12</v>
       </c>
     </row>
-    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>323</v>
+        <v>54</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2711,7 +1845,7 @@
         <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>17</v>
@@ -2723,35 +1857,33 @@
         <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>30</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{799F2BD1-FD78-448F-ADE0-45642B43D84A}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C8655E4-5A57-47F0-9C21-BF6A0B57A685}">
+  <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="26.0" collapsed="true"/>
+    <col min="2" max="2" width="26.33203125" bestFit="1" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2795,19 +1927,19 @@
         <v>12</v>
       </c>
     </row>
-    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>347</v>
+        <v>33</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>16</v>
@@ -2825,11 +1957,9 @@
         <v>20</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
         <v>23</v>
       </c>
@@ -2837,17 +1967,59 @@
         <v>25</v>
       </c>
     </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29FE3965-D54B-4EAB-9FD8-877E447C190D}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A154E49-E158-4463-B5C3-6CDEA93CBDB2}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="26.33203125" bestFit="1" customWidth="1" collapsed="1"/>
+  </cols>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2891,19 +2063,19 @@
         <v>12</v>
       </c>
     </row>
-    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>345</v>
+        <v>58</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>16</v>
@@ -2918,35 +2090,30 @@
         <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>30</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9AD100D-0DBC-45F3-A121-6F02543E9C7F}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12A8FA97-EA94-460D-9BF0-5144B0920793}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="23.77734375" collapsed="true"/>
-  </cols>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2995,24 +2162,26 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>278</v>
+        <v>58</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="1"/>
+      <c r="H2" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="I2" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>20</v>
@@ -3022,23 +2191,23 @@
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0B1942B-E20C-4A56-9017-395FE3466CCA}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5E82AC4-0DD3-4A6C-8764-98300EA23602}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3087,50 +2256,52 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>279</v>
+        <v>58</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="1"/>
+      <c r="H2" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="I2" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>20</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{800664F6-7B82-4E54-A9A3-002FB30EA5CC}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1509C6D-AC54-4BC5-B08C-8DB2E742B7EE}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3179,50 +2350,52 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>325</v>
+        <v>58</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="1"/>
+      <c r="H2" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="I2" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AFA7D1E-C4C8-4F11-85C1-FED8E36A55A8}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D88B2F1-D044-4986-A02D-57CE88C4C5D8}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3271,24 +2444,26 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>281</v>
+        <v>58</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="1"/>
+      <c r="H2" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="I2" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>20</v>
@@ -3298,23 +2473,23 @@
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0002C261-402A-419B-8856-C464A90C3C50}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACEC2CC9-16AB-47E7-916A-C86EFB95B8FF}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3363,50 +2538,52 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>326</v>
+        <v>56</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="1"/>
+      <c r="H2" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="I2" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2342668C-48CF-464B-9A5B-74841457CAE0}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA6B971B-52E7-48F5-BA39-F48125D3BA0C}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3455,24 +2632,26 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="1"/>
+      <c r="H2" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="I2" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>18</v>
@@ -3482,23 +2661,117 @@
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92120825-7846-4C9C-88ED-92501CF95AED}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62C3F18C-9D20-495D-9813-3EBF52ED12D9}">
-  <dimension ref="A1:O3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62C3F18C-9D20-495D-9813-3EBF52ED12D9}">
+  <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3547,7 +2820,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>328</v>
+        <v>48</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3619,16 +2892,987 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79778434-0500-4434-B2E5-7886F643688F}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A832AAC-8276-4369-BA73-CE01B795B95A}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAB20633-2C53-43C5-A793-14D961E78E27}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{799F2BD1-FD78-448F-ADE0-45642B43D84A}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="26" bestFit="1" customWidth="1" collapsed="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7742E74-BED5-4C78-8056-6C14AEEC36AB}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="26" bestFit="1" customWidth="1" collapsed="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA0FBC89-D585-490C-A35F-1BF87EF3B170}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="26" bestFit="1" customWidth="1" collapsed="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96D45AE6-C9E5-47E7-B8DF-3089D98C9CF6}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="26" bestFit="1" customWidth="1" collapsed="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{832DC3FA-603A-4979-AD71-E897EC3ED97B}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="26" bestFit="1" customWidth="1" collapsed="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29FE3965-D54B-4EAB-9FD8-877E447C190D}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9B81EC9-BFA3-4ADB-80C7-A1741C67E606}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2966B24D-47B9-4F80-A7B5-23FEBF76DFC5}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2A76537-B4E7-49D9-BB6B-6BEBB487994C}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3677,7 +3921,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3709,20 +3953,866 @@
         <v>18</v>
       </c>
       <c r="N2" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{397EE737-CEF3-494B-A795-96F89F13137F}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54EB7E56-4EAB-4CD6-A3A8-A0A4BB218F38}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BE3AEF6-CC99-4A22-BCE8-6029D4C3E422}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9AD100D-0DBC-45F3-A121-6F02543E9C7F}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="23.77734375" bestFit="1" customWidth="1" collapsed="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0B1942B-E20C-4A56-9017-395FE3466CCA}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{800664F6-7B82-4E54-A9A3-002FB30EA5CC}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AFA7D1E-C4C8-4F11-85C1-FED8E36A55A8}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0002C261-402A-419B-8856-C464A90C3C50}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2342668C-48CF-464B-9A5B-74841457CAE0}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C787DE57-842A-41F3-A622-37CAD141F86A}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B6ADA8A-7EE4-40F6-938E-0A306DE4B15B}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="8.44140625" bestFit="1" customWidth="1" collapsed="1"/>
+  </cols>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3771,7 +4861,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>332</v>
+        <v>67</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3781,7 +4871,7 @@
         <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>17</v>
@@ -3803,20 +4893,23 @@
         <v>23</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4D9E566-D549-4290-8382-839D19B358D4}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAFC1E22-20C9-4E63-A1A2-4C06141A245A}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="5" max="5" width="8.44140625" bestFit="1" customWidth="1" collapsed="1"/>
+  </cols>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3865,7 +4958,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>333</v>
+        <v>67</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3875,7 +4968,7 @@
         <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>17</v>
@@ -3890,27 +4983,27 @@
         <v>20</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06A1626C-D7FE-41AC-B701-168C96807B23}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2966B24D-47B9-4F80-A7B5-23FEBF76DFC5}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3959,7 +5052,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>331</v>
+        <v>35</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3969,7 +5062,7 @@
         <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>17</v>
@@ -3991,20 +5084,20 @@
         <v>18</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BDBB12C-A1A3-4DC3-80BE-B879BD79EAD4}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F23804EF-1C28-4E7F-965B-9364292CD6F8}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4049,12 +5142,6 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" t="s">
-        <v>284</v>
-      </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
@@ -4063,7 +5150,7 @@
         <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>17</v>
@@ -4075,30 +5162,30 @@
         <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C84570EB-6A55-4CD3-91DD-65D15A5DA7B9}">
-  <dimension ref="A1:O2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C787DE57-842A-41F3-A622-37CAD141F86A}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4147,7 +5234,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>327</v>
+        <v>52</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4157,7 +5244,7 @@
         <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>17</v>
@@ -4172,17 +5259,17 @@
         <v>20</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/KatalonData/IWPBootstrapData/vRelayPaymentsACH.xlsx
+++ b/KatalonData/IWPBootstrapData/vRelayPaymentsACH.xlsx
@@ -1,70 +1,70 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476046\Documents\VPS-Katalon-feature-VRelay\KatalonData\IWPBootstrapData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABD0496D-E0D4-44AE-A8C2-30962159A40A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr documentId="13_ncr:1_{ABD0496D-E0D4-44AE-A8C2-30962159A40A}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="4" firstSheet="3" windowHeight="12456" windowWidth="23256" xWindow="-108" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-108"/>
   </bookViews>
   <sheets>
-    <sheet name="PayNowNoCFPC" sheetId="1" r:id="rId1"/>
-    <sheet name="PayNowNoCFPS" sheetId="2" r:id="rId2"/>
-    <sheet name="PayNowNoCFCorp" sheetId="3" r:id="rId3"/>
-    <sheet name="VerifyPaymentConfCorp" sheetId="45" r:id="rId4"/>
-    <sheet name="VerifyPaymentReceiptPC" sheetId="49" r:id="rId5"/>
-    <sheet name="VerifyPaymentConfPC" sheetId="46" r:id="rId6"/>
-    <sheet name="PayNowCorpNoCF" sheetId="28" r:id="rId7"/>
-    <sheet name="VerifyPaymentReceiptCorp" sheetId="48" r:id="rId8"/>
-    <sheet name="PayNowSCFPC" sheetId="4" r:id="rId9"/>
-    <sheet name="PayNowSCFPS" sheetId="5" r:id="rId10"/>
-    <sheet name="PayNowSCFCorp" sheetId="6" r:id="rId11"/>
-    <sheet name="PayNowDCFPC" sheetId="7" r:id="rId12"/>
-    <sheet name="PayNowDCFPS" sheetId="8" r:id="rId13"/>
-    <sheet name="PayNowDCFCorp" sheetId="9" r:id="rId14"/>
-    <sheet name="SCFPSVerbiage" sheetId="10" r:id="rId15"/>
-    <sheet name="SCFPCVerbiage" sheetId="11" r:id="rId16"/>
-    <sheet name="SCFCorpVerbiage" sheetId="12" r:id="rId17"/>
-    <sheet name="DCFPSVerbiage" sheetId="13" r:id="rId18"/>
-    <sheet name="DCFPCVerbiage" sheetId="14" r:id="rId19"/>
-    <sheet name="DCFCorpVerbiage" sheetId="15" r:id="rId20"/>
-    <sheet name="CMCAutopayPS" sheetId="16" r:id="rId21"/>
-    <sheet name="CMCAutoPayPC" sheetId="17" r:id="rId22"/>
-    <sheet name="CancelStaticTextAutopayPC" sheetId="37" r:id="rId23"/>
-    <sheet name="CancelSuccessAutopayPC" sheetId="38" r:id="rId24"/>
-    <sheet name="ModifyStaticTextAutopayPC" sheetId="39" r:id="rId25"/>
-    <sheet name="ModifySuccessAutopayPC" sheetId="40" r:id="rId26"/>
-    <sheet name="CMCAutoPayCorp" sheetId="18" r:id="rId27"/>
-    <sheet name="CancelStaticTextAutoPayCorp" sheetId="29" r:id="rId28"/>
-    <sheet name="CancelSuccessAutoPayCorp" sheetId="30" r:id="rId29"/>
-    <sheet name="ModifyStaticTextAutopayCorp" sheetId="31" r:id="rId30"/>
-    <sheet name="ModifySuccessAutopayCorp" sheetId="32" r:id="rId31"/>
-    <sheet name="CCDeferredPS" sheetId="19" r:id="rId32"/>
-    <sheet name="CCDeferredPC" sheetId="20" r:id="rId33"/>
-    <sheet name="CancelStaticTextDeferredPC" sheetId="41" r:id="rId34"/>
-    <sheet name="CancelSuccessDeferredPC" sheetId="42" r:id="rId35"/>
-    <sheet name="ModifyStaticTextDeferredPC" sheetId="43" r:id="rId36"/>
-    <sheet name="ModifySuccessDeferredPC" sheetId="44" r:id="rId37"/>
-    <sheet name="CCDeferredCorp" sheetId="21" r:id="rId38"/>
-    <sheet name="CancelStaticTextDeferredCorp" sheetId="33" r:id="rId39"/>
-    <sheet name="CancelSuccessDeferredCorp" sheetId="34" r:id="rId40"/>
-    <sheet name="ModifyStaticTextDeferredCorp" sheetId="35" r:id="rId41"/>
-    <sheet name="ModifySuccessDeferredCorp" sheetId="36" r:id="rId42"/>
-    <sheet name="NoModifyAmountPC" sheetId="22" r:id="rId43"/>
-    <sheet name="NoModifyAmountPS" sheetId="23" r:id="rId44"/>
-    <sheet name="NoModifyAmountCorp" sheetId="24" r:id="rId45"/>
-    <sheet name="NoModifyBillingAddressPC" sheetId="25" r:id="rId46"/>
-    <sheet name="NoModifyBillingAddressPS" sheetId="26" r:id="rId47"/>
-    <sheet name="NoModifyBillingAddressCorp" sheetId="27" r:id="rId48"/>
+    <sheet name="PayNowNoCFPC" r:id="rId1" sheetId="1"/>
+    <sheet name="PayNowNoCFPS" r:id="rId2" sheetId="2"/>
+    <sheet name="PayNowNoCFCorp" r:id="rId3" sheetId="3"/>
+    <sheet name="VerifyPaymentConfCorp" r:id="rId4" sheetId="45"/>
+    <sheet name="VerifyPaymentReceiptPC" r:id="rId5" sheetId="49"/>
+    <sheet name="VerifyPaymentConfPC" r:id="rId6" sheetId="46"/>
+    <sheet name="PayNowCorpNoCF" r:id="rId7" sheetId="28"/>
+    <sheet name="VerifyPaymentReceiptCorp" r:id="rId8" sheetId="48"/>
+    <sheet name="PayNowSCFPC" r:id="rId9" sheetId="4"/>
+    <sheet name="PayNowSCFPS" r:id="rId10" sheetId="5"/>
+    <sheet name="PayNowSCFCorp" r:id="rId11" sheetId="6"/>
+    <sheet name="PayNowDCFPC" r:id="rId12" sheetId="7"/>
+    <sheet name="PayNowDCFPS" r:id="rId13" sheetId="8"/>
+    <sheet name="PayNowDCFCorp" r:id="rId14" sheetId="9"/>
+    <sheet name="SCFPSVerbiage" r:id="rId15" sheetId="10"/>
+    <sheet name="SCFPCVerbiage" r:id="rId16" sheetId="11"/>
+    <sheet name="SCFCorpVerbiage" r:id="rId17" sheetId="12"/>
+    <sheet name="DCFPSVerbiage" r:id="rId18" sheetId="13"/>
+    <sheet name="DCFPCVerbiage" r:id="rId19" sheetId="14"/>
+    <sheet name="DCFCorpVerbiage" r:id="rId20" sheetId="15"/>
+    <sheet name="CMCAutopayPS" r:id="rId21" sheetId="16"/>
+    <sheet name="CMCAutoPayPC" r:id="rId22" sheetId="17"/>
+    <sheet name="CancelStaticTextAutopayPC" r:id="rId23" sheetId="37"/>
+    <sheet name="CancelSuccessAutopayPC" r:id="rId24" sheetId="38"/>
+    <sheet name="ModifyStaticTextAutopayPC" r:id="rId25" sheetId="39"/>
+    <sheet name="ModifySuccessAutopayPC" r:id="rId26" sheetId="40"/>
+    <sheet name="CMCAutoPayCorp" r:id="rId27" sheetId="18"/>
+    <sheet name="CancelStaticTextAutoPayCorp" r:id="rId28" sheetId="29"/>
+    <sheet name="CancelSuccessAutoPayCorp" r:id="rId29" sheetId="30"/>
+    <sheet name="ModifyStaticTextAutopayCorp" r:id="rId30" sheetId="31"/>
+    <sheet name="ModifySuccessAutopayCorp" r:id="rId31" sheetId="32"/>
+    <sheet name="CCDeferredPS" r:id="rId32" sheetId="19"/>
+    <sheet name="CCDeferredPC" r:id="rId33" sheetId="20"/>
+    <sheet name="CancelStaticTextDeferredPC" r:id="rId34" sheetId="41"/>
+    <sheet name="CancelSuccessDeferredPC" r:id="rId35" sheetId="42"/>
+    <sheet name="ModifyStaticTextDeferredPC" r:id="rId36" sheetId="43"/>
+    <sheet name="ModifySuccessDeferredPC" r:id="rId37" sheetId="44"/>
+    <sheet name="CCDeferredCorp" r:id="rId38" sheetId="21"/>
+    <sheet name="CancelStaticTextDeferredCorp" r:id="rId39" sheetId="33"/>
+    <sheet name="CancelSuccessDeferredCorp" r:id="rId40" sheetId="34"/>
+    <sheet name="ModifyStaticTextDeferredCorp" r:id="rId41" sheetId="35"/>
+    <sheet name="ModifySuccessDeferredCorp" r:id="rId42" sheetId="36"/>
+    <sheet name="NoModifyAmountPC" r:id="rId43" sheetId="22"/>
+    <sheet name="NoModifyAmountPS" r:id="rId44" sheetId="23"/>
+    <sheet name="NoModifyAmountCorp" r:id="rId45" sheetId="24"/>
+    <sheet name="NoModifyBillingAddressPC" r:id="rId46" sheetId="25"/>
+    <sheet name="NoModifyBillingAddressPS" r:id="rId47" sheetId="26"/>
+    <sheet name="NoModifyBillingAddressCorp" r:id="rId48" sheetId="27"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1283" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="201">
   <si>
     <t>Result</t>
   </si>
@@ -276,12 +276,412 @@
   </si>
   <si>
     <t>Mon Apr 06 21:44:56 IST 2026</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Fri Apr 24 22:21:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 22:23:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 22:25:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 22:27:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 22:29:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 22:31:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 22:32:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 22:34:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 22:37:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 22:38:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 22:40:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 22:44:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 22:45:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 22:46:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 22:48:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 22:49:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 22:52:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 22:53:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 22:54:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 23:01:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 23:02:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 23:03:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 23:05:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 23:06:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 23:07:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 23:11:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 23:13:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 23:15:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 23:17:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 23:19:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 23:25:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 23:30:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 23:35:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 23:36:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 23:36:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 23:37:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 23:37:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 23:38:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 23:38:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 23:43:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 23:44:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 23:45:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 23:45:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 23:46:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Apr 24 23:47:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 20:12:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 20:16:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 20:19:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 20:22:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 21:40:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 21:44:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Apr 27 23:48:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 20:51:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri May 01 22:01:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 21:46:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 21:49:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 21:51:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 21:54:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 21:55:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 21:56:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:00:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:01:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:02:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:04:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:05:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:08:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:09:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:10:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:18:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:19:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:20:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:22:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:23:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:24:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:26:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:28:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:30:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:32:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:34:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:35:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:42:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:44:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:46:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:47:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:49:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:58:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 22:59:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:00:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:00:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:00:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:07:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:08:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:09:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:16:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:18:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:26:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:28:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:31:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:32:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:35:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:36:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:38:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:40:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:42:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:43:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:45:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:47:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:50:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:51:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:53:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:55:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 02 23:56:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 04 20:23:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 04 20:38:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 04 20:43:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 00:25:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 00:52:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 00:56:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 01:00:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 01:03:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 01:05:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 01:09:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 14:58:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 15:25:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 15:29:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 15:33:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 15:36:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 15:37:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 15:41:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 23:47:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 00:59:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 01:00:12 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -324,21 +724,21 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0"/>
+    <xf applyBorder="1" borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle builtinId="0" name="Normal" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -355,10 +755,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -393,7 +793,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -428,7 +828,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -522,21 +922,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -553,7 +953,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -605,21 +1005,21 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="8.44140625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="8.44140625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -668,7 +1068,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>138</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -704,7 +1104,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -712,11 +1112,11 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4D9E566-D549-4290-8382-839D19B358D4}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4D9E566-D549-4290-8382-839D19B358D4}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -765,7 +1165,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -801,16 +1201,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06A1626C-D7FE-41AC-B701-168C96807B23}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06A1626C-D7FE-41AC-B701-168C96807B23}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -859,7 +1259,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>140</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -895,16 +1295,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BDBB12C-A1A3-4DC3-80BE-B879BD79EAD4}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BDBB12C-A1A3-4DC3-80BE-B879BD79EAD4}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -953,7 +1353,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>135</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -989,16 +1389,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C84570EB-6A55-4CD3-91DD-65D15A5DA7B9}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C84570EB-6A55-4CD3-91DD-65D15A5DA7B9}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1047,7 +1447,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>136</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1083,16 +1483,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11E0D7D6-07EB-4231-93F6-ED08F4FB8116}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11E0D7D6-07EB-4231-93F6-ED08F4FB8116}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1141,7 +1541,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>134</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1177,16 +1577,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4906B75B-52A2-4286-8E49-5AC0D3846EF6}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4906B75B-52A2-4286-8E49-5AC0D3846EF6}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1235,7 +1635,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>199</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1271,16 +1671,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A8CFE94-49D0-484F-8EA4-D25F286F5569}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A8CFE94-49D0-484F-8EA4-D25F286F5569}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1329,7 +1729,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>160</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1365,16 +1765,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAAC6231-DFFA-4867-A2C5-E804FC85451E}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAAC6231-DFFA-4867-A2C5-E804FC85451E}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1423,7 +1823,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>159</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1459,16 +1859,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F82C58E-06FC-4FC1-A08F-B42071E415C5}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F82C58E-06FC-4FC1-A08F-B42071E415C5}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1517,7 +1917,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>158</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1553,16 +1953,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1142462-EBF3-4DC6-A60C-82C83F380CA2}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1142462-EBF3-4DC6-A60C-82C83F380CA2}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1611,7 +2011,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>155</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1647,16 +2047,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31792679-2814-4031-94D5-F81C214E87F1}">
-  <dimension ref="A1:N3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31792679-2814-4031-94D5-F81C214E87F1}">
+  <dimension ref="A1:O3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1705,7 +2105,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>139</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1777,16 +2177,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADDD6D56-27E0-426C-B504-18A7A35ECE43}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADDD6D56-27E0-426C-B504-18A7A35ECE43}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1835,7 +2235,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>154</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1871,19 +2271,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C8655E4-5A57-47F0-9C21-BF6A0B57A685}">
-  <dimension ref="A1:N3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C8655E4-5A57-47F0-9C21-BF6A0B57A685}">
+  <dimension ref="A1:O3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.33203125" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="26.33203125" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1972,7 +2372,7 @@
         <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
@@ -2007,19 +2407,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A154E49-E158-4463-B5C3-6CDEA93CBDB2}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A154E49-E158-4463-B5C3-6CDEA93CBDB2}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.33203125" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="26.33203125" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2068,7 +2468,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>175</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2104,16 +2504,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12A8FA97-EA94-460D-9BF0-5144B0920793}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12A8FA97-EA94-460D-9BF0-5144B0920793}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2162,7 +2562,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>181</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2198,16 +2598,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5E82AC4-0DD3-4A6C-8764-98300EA23602}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5E82AC4-0DD3-4A6C-8764-98300EA23602}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2256,7 +2656,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>163</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2292,16 +2692,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1509C6D-AC54-4BC5-B08C-8DB2E742B7EE}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1509C6D-AC54-4BC5-B08C-8DB2E742B7EE}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2350,7 +2750,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>183</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2386,16 +2786,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D88B2F1-D044-4986-A02D-57CE88C4C5D8}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D88B2F1-D044-4986-A02D-57CE88C4C5D8}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2444,7 +2844,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>165</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2480,16 +2880,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACEC2CC9-16AB-47E7-916A-C86EFB95B8FF}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACEC2CC9-16AB-47E7-916A-C86EFB95B8FF}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2538,7 +2938,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>174</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2574,16 +2974,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA6B971B-52E7-48F5-BA39-F48125D3BA0C}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA6B971B-52E7-48F5-BA39-F48125D3BA0C}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2632,7 +3032,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>144</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2668,16 +3068,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92120825-7846-4C9C-88ED-92501CF95AED}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92120825-7846-4C9C-88ED-92501CF95AED}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2726,7 +3126,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>162</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2762,16 +3162,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62C3F18C-9D20-495D-9813-3EBF52ED12D9}">
-  <dimension ref="A1:N3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62C3F18C-9D20-495D-9813-3EBF52ED12D9}">
+  <dimension ref="A1:O3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2820,7 +3220,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>137</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2892,16 +3292,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79778434-0500-4434-B2E5-7886F643688F}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79778434-0500-4434-B2E5-7886F643688F}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2950,7 +3350,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>182</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2986,16 +3386,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A832AAC-8276-4369-BA73-CE01B795B95A}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A832AAC-8276-4369-BA73-CE01B795B95A}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3044,7 +3444,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>164</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3080,16 +3480,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAB20633-2C53-43C5-A793-14D961E78E27}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAB20633-2C53-43C5-A793-14D961E78E27}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3133,12 +3533,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>128</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3176,19 +3576,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{799F2BD1-FD78-448F-ADE0-45642B43D84A}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{799F2BD1-FD78-448F-ADE0-45642B43D84A}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="26.0" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3232,12 +3632,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3275,19 +3675,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7742E74-BED5-4C78-8056-6C14AEEC36AB}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7742E74-BED5-4C78-8056-6C14AEEC36AB}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="26.0" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3331,12 +3731,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>192</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3374,19 +3774,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA0FBC89-D585-490C-A35F-1BF87EF3B170}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA0FBC89-D585-490C-A35F-1BF87EF3B170}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="26.0" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3430,12 +3830,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>193</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3473,19 +3873,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96D45AE6-C9E5-47E7-B8DF-3089D98C9CF6}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96D45AE6-C9E5-47E7-B8DF-3089D98C9CF6}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="26.0" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3529,12 +3929,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>194</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3572,19 +3972,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{832DC3FA-603A-4979-AD71-E897EC3ED97B}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{832DC3FA-603A-4979-AD71-E897EC3ED97B}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="26.0" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3628,12 +4028,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>196</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3671,16 +4071,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29FE3965-D54B-4EAB-9FD8-877E447C190D}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29FE3965-D54B-4EAB-9FD8-877E447C190D}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3724,12 +4124,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>200</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3767,16 +4167,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9B81EC9-BFA3-4ADB-80C7-A1741C67E606}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9B81EC9-BFA3-4ADB-80C7-A1741C67E606}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3820,12 +4220,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>166</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3863,16 +4263,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2A76537-B4E7-49D9-BB6B-6BEBB487994C}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2A76537-B4E7-49D9-BB6B-6BEBB487994C}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3921,7 +4321,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>177</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3957,16 +4357,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{397EE737-CEF3-494B-A795-96F89F13137F}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{397EE737-CEF3-494B-A795-96F89F13137F}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4010,12 +4410,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>198</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4053,16 +4453,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54EB7E56-4EAB-4CD6-A3A8-A0A4BB218F38}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54EB7E56-4EAB-4CD6-A3A8-A0A4BB218F38}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4106,12 +4506,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>170</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4149,16 +4549,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BE3AEF6-CC99-4A22-BCE8-6029D4C3E422}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BE3AEF6-CC99-4A22-BCE8-6029D4C3E422}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4202,12 +4602,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>195</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4245,19 +4645,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9AD100D-0DBC-45F3-A121-6F02543E9C7F}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9AD100D-0DBC-45F3-A121-6F02543E9C7F}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="23.77734375" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="23.77734375" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4306,7 +4706,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4340,16 +4740,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0B1942B-E20C-4A56-9017-395FE3466CCA}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0B1942B-E20C-4A56-9017-395FE3466CCA}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4398,7 +4798,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>131</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4432,16 +4832,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{800664F6-7B82-4E54-A9A3-002FB30EA5CC}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{800664F6-7B82-4E54-A9A3-002FB30EA5CC}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4490,7 +4890,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>129</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4524,16 +4924,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AFA7D1E-C4C8-4F11-85C1-FED8E36A55A8}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AFA7D1E-C4C8-4F11-85C1-FED8E36A55A8}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4582,7 +4982,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>133</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4616,16 +5016,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0002C261-402A-419B-8856-C464A90C3C50}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0002C261-402A-419B-8856-C464A90C3C50}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4674,7 +5074,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>191</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4708,16 +5108,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2342668C-48CF-464B-9A5B-74841457CAE0}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2342668C-48CF-464B-9A5B-74841457CAE0}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4766,7 +5166,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4800,19 +5200,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B6ADA8A-7EE4-40F6-938E-0A306DE4B15B}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B6ADA8A-7EE4-40F6-938E-0A306DE4B15B}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="8.44140625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="8.44140625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4861,7 +5261,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>180</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4897,19 +5297,19 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAFC1E22-20C9-4E63-A1A2-4C06141A245A}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAFC1E22-20C9-4E63-A1A2-4C06141A245A}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="8.44140625" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="8.44140625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4958,7 +5358,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>197</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4994,16 +5394,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2966B24D-47B9-4F80-A7B5-23FEBF76DFC5}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2966B24D-47B9-4F80-A7B5-23FEBF76DFC5}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5088,16 +5488,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F23804EF-1C28-4E7F-965B-9364292CD6F8}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F23804EF-1C28-4E7F-965B-9364292CD6F8}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5142,6 +5542,12 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>179</v>
+      </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
         <v>14</v>
@@ -5176,16 +5582,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C787DE57-842A-41F3-A622-37CAD141F86A}">
-  <dimension ref="A1:N2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C787DE57-842A-41F3-A622-37CAD141F86A}">
+  <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5234,7 +5640,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>141</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5270,6 +5676,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/KatalonData/IWPBootstrapData/vRelayPaymentsACH.xlsx
+++ b/KatalonData/IWPBootstrapData/vRelayPaymentsACH.xlsx
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2199" uniqueCount="298">
   <si>
     <t>Result</t>
   </si>
@@ -675,6 +675,297 @@
   </si>
   <si>
     <t>Wed May 06 01:00:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:17:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:44:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:48:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:52:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:55:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 01:56:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat May 30 02:00:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 21:18:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 01 21:20:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:03:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:05:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:07:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:13:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:15:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:16:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:17:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:18:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:19:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:20:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:22:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:23:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:24:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:25:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:26:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:33:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:34:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:35:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:37:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:38:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:41:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:42:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:43:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:50:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:51:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:52:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:54:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:55:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:56:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 04 23:59:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 00:01:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 00:07:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 00:09:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 00:15:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 00:16:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 00:20:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 00:23:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 00:23:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 00:24:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 00:29:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 00:30:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 00:31:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 00:37:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 00:39:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 00:41:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 00:43:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 00:45:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 00:46:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 00:53:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 00:57:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:00:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:01:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:03:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:04:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:10:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:12:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:13:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:14:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:15:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:17:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:18:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:19:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:26:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:27:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:29:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:30:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:31:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:32:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:34:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:35:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:36:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:40:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:41:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:43:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:45:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:49:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:50:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:51:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:54:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jun 05 01:55:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 00:55:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 01:30:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 01:31:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 01:32:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 01:34:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jun 06 01:35:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 20:26:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 08 21:02:56 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1068,7 +1359,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>138</v>
+        <v>234</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1165,7 +1456,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>142</v>
+        <v>238</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1259,7 +1550,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>140</v>
+        <v>236</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1353,7 +1644,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>135</v>
+        <v>231</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1447,7 +1738,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>136</v>
+        <v>232</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1541,7 +1832,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>134</v>
+        <v>230</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1635,7 +1926,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>199</v>
+        <v>291</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1729,7 +2020,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>160</v>
+        <v>250</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1823,7 +2114,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>159</v>
+        <v>249</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1917,7 +2208,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>158</v>
+        <v>248</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2011,7 +2302,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>155</v>
+        <v>247</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2105,7 +2396,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>139</v>
+        <v>235</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2235,7 +2526,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>154</v>
+        <v>246</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2372,7 +2663,7 @@
         <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>125</v>
+        <v>212</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
@@ -2468,7 +2759,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>175</v>
+        <v>284</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2562,7 +2853,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>181</v>
+        <v>240</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2656,7 +2947,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>163</v>
+        <v>257</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2750,7 +3041,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>183</v>
+        <v>245</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2844,7 +3135,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>165</v>
+        <v>259</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -2938,7 +3229,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>174</v>
+        <v>280</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3032,7 +3323,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>144</v>
+        <v>239</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3126,7 +3417,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>162</v>
+        <v>253</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3220,7 +3511,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>137</v>
+        <v>233</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3347,10 +3638,10 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>182</v>
+        <v>242</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3444,7 +3735,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>164</v>
+        <v>258</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3538,7 +3829,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>128</v>
+        <v>224</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3637,7 +3928,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>127</v>
+        <v>220</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3736,7 +4027,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>192</v>
+        <v>261</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3835,7 +4126,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>193</v>
+        <v>263</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -3934,7 +4225,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>194</v>
+        <v>271</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4033,7 +4324,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>196</v>
+        <v>279</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4129,7 +4420,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>200</v>
+        <v>297</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4225,7 +4516,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>166</v>
+        <v>260</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4321,7 +4612,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>177</v>
+        <v>286</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4415,7 +4706,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>198</v>
+        <v>290</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4511,7 +4802,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>170</v>
+        <v>267</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4607,7 +4898,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>195</v>
+        <v>275</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4706,7 +4997,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>130</v>
+        <v>226</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4798,7 +5089,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>131</v>
+        <v>227</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4890,7 +5181,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>129</v>
+        <v>225</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -4982,7 +5273,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>133</v>
+        <v>229</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5074,7 +5365,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5166,7 +5457,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>132</v>
+        <v>228</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5261,7 +5552,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>180</v>
+        <v>289</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5358,7 +5649,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>197</v>
+        <v>287</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5546,7 +5837,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>179</v>
+        <v>288</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -5640,7 +5931,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>141</v>
+        <v>237</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">

--- a/KatalonData/IWPBootstrapData/vRelayPaymentsACH.xlsx
+++ b/KatalonData/IWPBootstrapData/vRelayPaymentsACH.xlsx
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2199" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2201" uniqueCount="299">
   <si>
     <t>Result</t>
   </si>
@@ -966,6 +966,9 @@
   </si>
   <si>
     <t>Mon Jun 08 21:02:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jun 24 15:25:41 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -1304,7 +1307,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="5" bestFit="true" customWidth="true" width="8.44140625" collapsed="true"/>
@@ -1355,11 +1358,11 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
-        <v>234</v>
+      <c r="B2" t="s" s="0">
+        <v>298</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="1" t="s">
@@ -1404,7 +1407,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4D9E566-D549-4290-8382-839D19B358D4}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -1452,10 +1455,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>238</v>
       </c>
       <c r="C2" s="3"/>
@@ -1498,7 +1501,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06A1626C-D7FE-41AC-B701-168C96807B23}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -1546,10 +1549,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>236</v>
       </c>
       <c r="C2" s="3"/>
@@ -1592,7 +1595,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BDBB12C-A1A3-4DC3-80BE-B879BD79EAD4}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -1640,10 +1643,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>231</v>
       </c>
       <c r="C2" s="3"/>
@@ -1686,7 +1689,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C84570EB-6A55-4CD3-91DD-65D15A5DA7B9}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -1734,10 +1737,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>232</v>
       </c>
       <c r="C2" s="3"/>
@@ -1780,7 +1783,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11E0D7D6-07EB-4231-93F6-ED08F4FB8116}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -1828,10 +1831,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>230</v>
       </c>
       <c r="C2" s="3"/>
@@ -1874,7 +1877,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4906B75B-52A2-4286-8E49-5AC0D3846EF6}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -1922,10 +1925,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>291</v>
       </c>
       <c r="C2" s="3"/>
@@ -1968,7 +1971,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A8CFE94-49D0-484F-8EA4-D25F286F5569}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -2016,10 +2019,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>250</v>
       </c>
       <c r="C2" s="3"/>
@@ -2062,7 +2065,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAAC6231-DFFA-4867-A2C5-E804FC85451E}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -2110,10 +2113,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>249</v>
       </c>
       <c r="C2" s="3"/>
@@ -2156,7 +2159,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F82C58E-06FC-4FC1-A08F-B42071E415C5}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -2204,10 +2207,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>248</v>
       </c>
       <c r="C2" s="3"/>
@@ -2250,7 +2253,7 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1142462-EBF3-4DC6-A60C-82C83F380CA2}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -2298,10 +2301,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>247</v>
       </c>
       <c r="C2" s="3"/>
@@ -2344,7 +2347,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31792679-2814-4031-94D5-F81C214E87F1}">
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -2392,10 +2395,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>235</v>
       </c>
       <c r="C2" s="3"/>
@@ -2474,7 +2477,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADDD6D56-27E0-426C-B504-18A7A35ECE43}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -2522,10 +2525,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>246</v>
       </c>
       <c r="C2" s="3"/>
@@ -2568,7 +2571,7 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C8655E4-5A57-47F0-9C21-BF6A0B57A685}">
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" bestFit="true" customWidth="true" width="26.33203125" collapsed="true"/>
@@ -2619,10 +2622,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>33</v>
       </c>
       <c r="C2" s="3"/>
@@ -2659,13 +2662,13 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
         <v>212</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" t="s" s="0">
         <v>14</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -2704,7 +2707,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A154E49-E158-4463-B5C3-6CDEA93CBDB2}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" bestFit="true" customWidth="true" width="26.33203125" collapsed="true"/>
@@ -2755,10 +2758,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>284</v>
       </c>
       <c r="C2" s="3"/>
@@ -2801,7 +2804,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12A8FA97-EA94-460D-9BF0-5144B0920793}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -2849,10 +2852,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>240</v>
       </c>
       <c r="C2" s="3"/>
@@ -2895,7 +2898,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5E82AC4-0DD3-4A6C-8764-98300EA23602}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -2943,10 +2946,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>257</v>
       </c>
       <c r="C2" s="3"/>
@@ -2989,7 +2992,7 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1509C6D-AC54-4BC5-B08C-8DB2E742B7EE}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -3037,10 +3040,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>245</v>
       </c>
       <c r="C2" s="3"/>
@@ -3083,7 +3086,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D88B2F1-D044-4986-A02D-57CE88C4C5D8}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -3131,10 +3134,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>259</v>
       </c>
       <c r="C2" s="3"/>
@@ -3177,7 +3180,7 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACEC2CC9-16AB-47E7-916A-C86EFB95B8FF}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -3225,10 +3228,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>280</v>
       </c>
       <c r="C2" s="3"/>
@@ -3271,7 +3274,7 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA6B971B-52E7-48F5-BA39-F48125D3BA0C}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -3319,10 +3322,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>239</v>
       </c>
       <c r="C2" s="3"/>
@@ -3365,7 +3368,7 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92120825-7846-4C9C-88ED-92501CF95AED}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -3413,10 +3416,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>253</v>
       </c>
       <c r="C2" s="3"/>
@@ -3459,7 +3462,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62C3F18C-9D20-495D-9813-3EBF52ED12D9}">
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -3507,10 +3510,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>233</v>
       </c>
       <c r="C2" s="3"/>
@@ -3589,7 +3592,7 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79778434-0500-4434-B2E5-7886F643688F}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -3637,10 +3640,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>242</v>
       </c>
       <c r="C2" s="3"/>
@@ -3683,7 +3686,7 @@
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A832AAC-8276-4369-BA73-CE01B795B95A}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -3731,10 +3734,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>258</v>
       </c>
       <c r="C2" s="3"/>
@@ -3777,7 +3780,7 @@
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAB20633-2C53-43C5-A793-14D961E78E27}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -3825,10 +3828,10 @@
       </c>
     </row>
     <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>224</v>
       </c>
       <c r="C2" s="3"/>
@@ -3873,7 +3876,7 @@
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{799F2BD1-FD78-448F-ADE0-45642B43D84A}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" bestFit="true" customWidth="true" width="26.0" collapsed="true"/>
@@ -3924,10 +3927,10 @@
       </c>
     </row>
     <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>220</v>
       </c>
       <c r="C2" s="3"/>
@@ -3972,7 +3975,7 @@
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7742E74-BED5-4C78-8056-6C14AEEC36AB}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" bestFit="true" customWidth="true" width="26.0" collapsed="true"/>
@@ -4023,10 +4026,10 @@
       </c>
     </row>
     <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>261</v>
       </c>
       <c r="C2" s="3"/>
@@ -4071,7 +4074,7 @@
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA0FBC89-D585-490C-A35F-1BF87EF3B170}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" bestFit="true" customWidth="true" width="26.0" collapsed="true"/>
@@ -4122,10 +4125,10 @@
       </c>
     </row>
     <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>263</v>
       </c>
       <c r="C2" s="3"/>
@@ -4170,7 +4173,7 @@
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96D45AE6-C9E5-47E7-B8DF-3089D98C9CF6}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" bestFit="true" customWidth="true" width="26.0" collapsed="true"/>
@@ -4221,10 +4224,10 @@
       </c>
     </row>
     <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>271</v>
       </c>
       <c r="C2" s="3"/>
@@ -4269,7 +4272,7 @@
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{832DC3FA-603A-4979-AD71-E897EC3ED97B}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" bestFit="true" customWidth="true" width="26.0" collapsed="true"/>
@@ -4320,10 +4323,10 @@
       </c>
     </row>
     <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>279</v>
       </c>
       <c r="C2" s="3"/>
@@ -4368,7 +4371,7 @@
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29FE3965-D54B-4EAB-9FD8-877E447C190D}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -4416,10 +4419,10 @@
       </c>
     </row>
     <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>297</v>
       </c>
       <c r="C2" s="3"/>
@@ -4464,7 +4467,7 @@
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9B81EC9-BFA3-4ADB-80C7-A1741C67E606}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -4512,10 +4515,10 @@
       </c>
     </row>
     <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>260</v>
       </c>
       <c r="C2" s="3"/>
@@ -4560,7 +4563,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2A76537-B4E7-49D9-BB6B-6BEBB487994C}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -4608,10 +4611,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>286</v>
       </c>
       <c r="C2" s="3"/>
@@ -4654,7 +4657,7 @@
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{397EE737-CEF3-494B-A795-96F89F13137F}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -4702,10 +4705,10 @@
       </c>
     </row>
     <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>290</v>
       </c>
       <c r="C2" s="3"/>
@@ -4750,7 +4753,7 @@
 
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54EB7E56-4EAB-4CD6-A3A8-A0A4BB218F38}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -4798,10 +4801,10 @@
       </c>
     </row>
     <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>267</v>
       </c>
       <c r="C2" s="3"/>
@@ -4846,7 +4849,7 @@
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BE3AEF6-CC99-4A22-BCE8-6029D4C3E422}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -4894,10 +4897,10 @@
       </c>
     </row>
     <row ht="28.8" r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>275</v>
       </c>
       <c r="C2" s="3"/>
@@ -4942,7 +4945,7 @@
 
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9AD100D-0DBC-45F3-A121-6F02543E9C7F}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" bestFit="true" customWidth="true" width="23.77734375" collapsed="true"/>
@@ -4993,10 +4996,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>226</v>
       </c>
       <c r="C2" s="3"/>
@@ -5037,7 +5040,7 @@
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0B1942B-E20C-4A56-9017-395FE3466CCA}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -5085,10 +5088,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>227</v>
       </c>
       <c r="C2" s="3"/>
@@ -5129,7 +5132,7 @@
 
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{800664F6-7B82-4E54-A9A3-002FB30EA5CC}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -5177,10 +5180,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>225</v>
       </c>
       <c r="C2" s="3"/>
@@ -5221,7 +5224,7 @@
 
 <file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AFA7D1E-C4C8-4F11-85C1-FED8E36A55A8}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -5269,10 +5272,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>229</v>
       </c>
       <c r="C2" s="3"/>
@@ -5313,7 +5316,7 @@
 
 <file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0002C261-402A-419B-8856-C464A90C3C50}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -5361,10 +5364,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>201</v>
       </c>
       <c r="C2" s="3"/>
@@ -5405,7 +5408,7 @@
 
 <file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2342668C-48CF-464B-9A5B-74841457CAE0}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -5453,10 +5456,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>228</v>
       </c>
       <c r="C2" s="3"/>
@@ -5497,7 +5500,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B6ADA8A-7EE4-40F6-938E-0A306DE4B15B}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="5" bestFit="true" customWidth="true" width="8.44140625" collapsed="true"/>
@@ -5548,10 +5551,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>289</v>
       </c>
       <c r="C2" s="3"/>
@@ -5594,7 +5597,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAFC1E22-20C9-4E63-A1A2-4C06141A245A}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="5" bestFit="true" customWidth="true" width="8.44140625" collapsed="true"/>
@@ -5645,10 +5648,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>287</v>
       </c>
       <c r="C2" s="3"/>
@@ -5691,7 +5694,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2966B24D-47B9-4F80-A7B5-23FEBF76DFC5}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -5739,10 +5742,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>35</v>
       </c>
       <c r="C2" s="3"/>
@@ -5785,7 +5788,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F23804EF-1C28-4E7F-965B-9364292CD6F8}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -5833,10 +5836,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>288</v>
       </c>
       <c r="C2" s="3"/>
@@ -5879,7 +5882,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C787DE57-842A-41F3-A622-37CAD141F86A}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row ht="28.8" r="1" spans="1:14" x14ac:dyDescent="0.3">
@@ -5927,10 +5930,10 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>237</v>
       </c>
       <c r="C2" s="3"/>
